--- a/Daily_Paid_payment_List_Aug_2026.xlsx
+++ b/Daily_Paid_payment_List_Aug_2026.xlsx
@@ -5,17 +5,23 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_Aug_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE5351D-6622-43D3-A329-83E6F7944FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF28CBB-10FF-4D30-8A94-7550D911F824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4845" yWindow="4410" windowWidth="18900" windowHeight="10965" activeTab="1" xr2:uid="{E1E8BEB0-7C45-40BF-B119-AC93F03CA3D8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{E1E8BEB0-7C45-40BF-B119-AC93F03CA3D8}"/>
   </bookViews>
   <sheets>
     <sheet name="date_01-08-2026 to 07-08-2026" sheetId="1" r:id="rId1"/>
     <sheet name="date_01-08-2026 to 14-08-2026" sheetId="2" r:id="rId2"/>
+    <sheet name="date_15-08-2026 to 21-08-2026" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'date_01-08-2026 to 07-08-2026'!$A$3:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'date_01-08-2026 to 14-08-2026'!$A$3:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'date_15-08-2026 to 21-08-2026'!$A$3:$G$3</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="100">
   <si>
     <t>M/S KRISHI INFRATECH,SOMPETA</t>
   </si>
@@ -308,13 +314,40 @@
   </si>
   <si>
     <t xml:space="preserve">  TOTAL</t>
+  </si>
+  <si>
+    <t>19-08-2026</t>
+  </si>
+  <si>
+    <t>Cello Tape 5 Nos for A1 Room</t>
+  </si>
+  <si>
+    <t>4" Grinding wheel &amp; 4" cutting wheel, cable for store, camp office work</t>
+  </si>
+  <si>
+    <t>Water can &amp; cloth for crusher weighment room</t>
+  </si>
+  <si>
+    <t>Wall fan for crusher weighment room</t>
+  </si>
+  <si>
+    <t>21-08-2026</t>
+  </si>
+  <si>
+    <t>Colin glass cleaner for office</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>G_381</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -374,8 +407,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -412,8 +450,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -447,11 +509,187 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -540,6 +778,117 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1358,6 +1707,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:G3" xr:uid="{B655872A-D0A9-4A11-BABC-8230FDBDB854}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1893,6 +2243,8 @@
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
     </row>
+    <row r="28" spans="1:7" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D30" s="24" t="s">
         <v>84</v>
@@ -2038,6 +2390,349 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:G3" xr:uid="{3453AA43-64B3-447F-9E4B-2EF455AA1368}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADAD385F-1EDD-42FB-88AE-5ED9F0917761}">
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="35.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="40"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="66"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="42"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="43"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="68"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="44"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="47"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="76">
+        <v>1130.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="48">
+        <v>140</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="34">
+        <v>186</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="36">
+        <v>165</v>
+      </c>
+      <c r="F5" s="33"/>
+      <c r="G5" s="49">
+        <f>G4-E5+F5</f>
+        <v>965.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="48">
+        <v>141</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="36">
+        <v>1025</v>
+      </c>
+      <c r="F6" s="36"/>
+      <c r="G6" s="49">
+        <f t="shared" ref="G6:G9" si="0">G5-E6+F6</f>
+        <v>-59.200000000000045</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="70">
+        <v>144</v>
+      </c>
+      <c r="B7" s="71" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="72"/>
+      <c r="D7" s="73" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74">
+        <v>10000</v>
+      </c>
+      <c r="G7" s="75">
+        <f t="shared" si="0"/>
+        <v>9940.7999999999993</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="48">
+        <v>145</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="34">
+        <v>396102</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="36">
+        <v>229</v>
+      </c>
+      <c r="F8" s="36"/>
+      <c r="G8" s="49">
+        <f t="shared" si="0"/>
+        <v>9711.7999999999993</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="43"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="49">
+        <f t="shared" si="0"/>
+        <v>9711.7999999999993</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="50"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" s="77"/>
+      <c r="E10" s="51">
+        <f>SUM(E4:E9)</f>
+        <v>1419</v>
+      </c>
+      <c r="F10" s="51">
+        <f>SUM(F4:F8)</f>
+        <v>10000</v>
+      </c>
+      <c r="G10" s="52">
+        <f>G9-E9+F9</f>
+        <v>9711.7999999999993</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="40"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="41"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="53"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="43"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="64" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="55"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" s="46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="56"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="76">
+        <v>9711.7999999999993</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="48">
+        <v>142</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="34">
+        <v>46</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="36">
+        <v>250</v>
+      </c>
+      <c r="F17" s="37"/>
+      <c r="G17" s="62">
+        <f>G16-E17+F17</f>
+        <v>9461.7999999999993</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="48">
+        <v>143</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="34">
+        <v>2088</v>
+      </c>
+      <c r="D18" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" s="36">
+        <v>2000</v>
+      </c>
+      <c r="F18" s="36"/>
+      <c r="G18" s="62">
+        <f t="shared" ref="G18:G20" si="1">G17-E18+F18</f>
+        <v>7461.7999999999993</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="48"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="62">
+        <f t="shared" si="1"/>
+        <v>7461.7999999999993</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="48"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="62">
+        <f t="shared" si="1"/>
+        <v>7461.7999999999993</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="57"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" s="60">
+        <f>SUM(E16:E20)</f>
+        <v>2250</v>
+      </c>
+      <c r="F21" s="60"/>
+      <c r="G21" s="61">
+        <f>G20-E20+F20</f>
+        <v>7461.7999999999993</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C24" s="65"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:G3" xr:uid="{ADAD385F-1EDD-42FB-88AE-5ED9F0917761}"/>
+  <mergeCells count="1">
+    <mergeCell ref="C10:D10"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>